--- a/mapdata_geocoded.xlsx
+++ b/mapdata_geocoded.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$347</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1015">
   <si>
     <t>순번</t>
   </si>
@@ -2746,15 +2746,6 @@
   </si>
   <si>
     <t>126.502111873467</t>
-  </si>
-  <si>
-    <t>전라남도 나주시 가마태길  38 (용산동, 용산주공아파트 1차상가 204호)</t>
-  </si>
-  <si>
-    <t>34.9943902228204</t>
-  </si>
-  <si>
-    <t>126.720712932062</t>
   </si>
   <si>
     <t>전라남도 영암군 금정면 여운재로  988-20 (금정면, (동행재가복지센터))</t>
@@ -3423,10 +3414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G348"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="54.75" customWidth="1"/>
+    <col min="4" max="4" width="93.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3530,7 +3521,7 @@
         <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -9635,13 +9626,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B311" t="s">
         <v>755</v>
       </c>
       <c r="C311" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D311" t="s">
         <v>908</v>
@@ -9655,7 +9646,7 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B312" t="s">
         <v>755</v>
@@ -9675,13 +9666,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B313" t="s">
         <v>755</v>
       </c>
       <c r="C313" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D313" t="s">
         <v>914</v>
@@ -9695,13 +9686,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B314" t="s">
         <v>755</v>
       </c>
       <c r="C314" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D314" t="s">
         <v>917</v>
@@ -9715,13 +9706,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B315" t="s">
         <v>755</v>
       </c>
       <c r="C315" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D315" t="s">
         <v>920</v>
@@ -9735,13 +9726,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B316" t="s">
         <v>755</v>
       </c>
       <c r="C316" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="D316" t="s">
         <v>923</v>
@@ -9755,13 +9746,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B317" t="s">
         <v>755</v>
       </c>
       <c r="C317" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="D317" t="s">
         <v>926</v>
@@ -9775,13 +9766,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B318" t="s">
         <v>755</v>
       </c>
       <c r="C318" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D318" t="s">
         <v>929</v>
@@ -9795,30 +9786,30 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="B319" t="s">
-        <v>755</v>
+        <v>932</v>
       </c>
       <c r="C319" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D319" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E319" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F319" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B320" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C320" t="s">
         <v>7</v>
@@ -9835,10 +9826,10 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B321" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C321" t="s">
         <v>7</v>
@@ -9855,10 +9846,10 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322">
-        <v>755</v>
+        <v>765</v>
       </c>
       <c r="B322" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C322" t="s">
         <v>7</v>
@@ -9875,10 +9866,10 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="B323" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C323" t="s">
         <v>7</v>
@@ -9895,10 +9886,10 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B324" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C324" t="s">
         <v>7</v>
@@ -9915,10 +9906,10 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B325" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C325" t="s">
         <v>7</v>
@@ -9927,41 +9918,41 @@
         <v>951</v>
       </c>
       <c r="E325" t="s">
-        <v>952</v>
+        <v>571</v>
       </c>
       <c r="F325" t="s">
-        <v>953</v>
+        <v>572</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B326" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C326" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="D326" t="s">
+        <v>952</v>
+      </c>
+      <c r="E326" t="s">
+        <v>953</v>
+      </c>
+      <c r="F326" t="s">
         <v>954</v>
-      </c>
-      <c r="E326" t="s">
-        <v>571</v>
-      </c>
-      <c r="F326" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="B327" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C327" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="D327" t="s">
         <v>955</v>
@@ -9975,10 +9966,10 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B328" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C328" t="s">
         <v>11</v>
@@ -9995,50 +9986,50 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B329" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C329" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D329" t="s">
         <v>961</v>
       </c>
       <c r="E329" t="s">
-        <v>962</v>
+        <v>640</v>
       </c>
       <c r="F329" t="s">
-        <v>963</v>
+        <v>641</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B330" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C330" t="s">
         <v>19</v>
       </c>
       <c r="D330" t="s">
+        <v>962</v>
+      </c>
+      <c r="E330" t="s">
+        <v>963</v>
+      </c>
+      <c r="F330" t="s">
         <v>964</v>
-      </c>
-      <c r="E330" t="s">
-        <v>640</v>
-      </c>
-      <c r="F330" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B331" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C331" t="s">
         <v>19</v>
@@ -10055,10 +10046,10 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B332" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C332" t="s">
         <v>19</v>
@@ -10075,10 +10066,10 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="B333" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C333" t="s">
         <v>19</v>
@@ -10095,10 +10086,10 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B334" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C334" t="s">
         <v>19</v>
@@ -10115,10 +10106,10 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B335" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C335" t="s">
         <v>19</v>
@@ -10135,10 +10126,10 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B336" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C336" t="s">
         <v>19</v>
@@ -10155,10 +10146,10 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B337" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C337" t="s">
         <v>19</v>
@@ -10175,13 +10166,13 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B338" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C338" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D338" t="s">
         <v>986</v>
@@ -10195,10 +10186,10 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B339" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C339" t="s">
         <v>7</v>
@@ -10215,10 +10206,10 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="B340" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C340" t="s">
         <v>7</v>
@@ -10235,10 +10226,10 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B341" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C341" t="s">
         <v>7</v>
@@ -10255,10 +10246,10 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B342" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C342" t="s">
         <v>7</v>
@@ -10275,53 +10266,53 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B343" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C343" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D343" t="s">
         <v>1001</v>
       </c>
       <c r="E343" t="s">
-        <v>1002</v>
+        <v>696</v>
       </c>
       <c r="F343" t="s">
-        <v>1003</v>
+        <v>697</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B344" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C344" t="s">
         <v>11</v>
       </c>
       <c r="D344" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F344" t="s">
         <v>1004</v>
-      </c>
-      <c r="E344" t="s">
-        <v>696</v>
-      </c>
-      <c r="F344" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B345" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C345" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D345" t="s">
         <v>1005</v>
@@ -10335,10 +10326,10 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B346" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C346" t="s">
         <v>19</v>
@@ -10355,10 +10346,10 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B347" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C347" t="s">
         <v>19</v>
@@ -10371,26 +10362,6 @@
       </c>
       <c r="F347" t="s">
         <v>1013</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A348">
-        <v>850</v>
-      </c>
-      <c r="B348" t="s">
-        <v>935</v>
-      </c>
-      <c r="C348" t="s">
-        <v>19</v>
-      </c>
-      <c r="D348" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1016</v>
       </c>
     </row>
   </sheetData>
